--- a/product_selector_out/STM32H730 value line.xlsx
+++ b/product_selector_out/STM32H730 value line.xlsx
@@ -4406,7 +4406,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 12. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 12. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 12. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 12. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 12. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 12. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 12. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 12. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32H730 value line.xlsx
+++ b/product_selector_out/STM32H730 value line.xlsx
@@ -1675,7 +1675,7 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h730ab.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3308,9 +3308,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -3373,14 +3373,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -3528,14 +3528,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY13" s="6" t="inlineStr">
@@ -3618,9 +3618,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4413,7 +4413,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32H730IB</t>
+          <t>STM32H730VB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4435,7 +4435,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32H730IB</t>
+          <t>STM32H730VB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4457,7 +4457,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32H730IB</t>
+          <t>STM32H730VB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4479,7 +4479,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32H730VB</t>
+          <t>STM32H730AB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4501,7 +4501,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32H730VB</t>
+          <t>STM32H730AB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4523,7 +4523,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32H730VB</t>
+          <t>STM32H730AB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4537,72 +4537,6 @@
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 12. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32H730AB</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32H730AB</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 4. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32H730AB</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
         <is>
           <t>Table 12. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>

--- a/product_selector_out/STM32H730 value line.xlsx
+++ b/product_selector_out/STM32H730 value line.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO15"/>
+  <dimension ref="A1:BP15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.65234375" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -907,6 +908,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1004,6 +1010,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1338,6 +1345,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h730ab.pdf</t>
         </is>
       </c>
@@ -1678,6 +1690,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2012,6 +2029,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h730ab.pdf</t>
         </is>
       </c>
@@ -2349,12 +2371,17 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h730ab.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -2377,12 +2404,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -2397,9 +2426,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -2439,7 +2467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO15"/>
+  <dimension ref="A1:BP15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2509,6 +2537,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2852,6 +2881,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -2949,6 +2983,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -3281,7 +3316,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -3623,6 +3663,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BP13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -3955,7 +4000,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4292,7 +4342,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4300,8 +4355,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
